--- a/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101034</t>
+          <t>100672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112645</t>
+          <t>112380</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>117736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216457</t>
+          <t>215898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222359</t>
+          <t>222328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120754</t>
+          <t>121212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129756</t>
+          <t>130259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138113</t>
+          <t>137671</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>253562</t>
+          <t>253117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261812</t>
+          <t>261840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>99993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106547</t>
+          <t>106590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103228</t>
+          <t>103084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110546</t>
+          <t>110503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>206427</t>
+          <t>206677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>215827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157445</t>
+          <t>157543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164538</t>
+          <t>164544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146993</t>
+          <t>146682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154288</t>
+          <t>154309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307857</t>
+          <t>307653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317496</t>
+          <t>317520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488610</t>
+          <t>488329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498524</t>
+          <t>498347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>502984</t>
+          <t>501929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516721</t>
+          <t>516409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>994541</t>
+          <t>995220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1011769</t>
+          <t>1012360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92851</t>
+          <t>94274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106013</t>
+          <t>105274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111834</t>
+          <t>111665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202061</t>
+          <t>201236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208320</t>
+          <t>208327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119090</t>
+          <t>118558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126325</t>
+          <t>126274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144035</t>
+          <t>143773</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151899</t>
+          <t>151815</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265837</t>
+          <t>265849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>276696</t>
+          <t>276660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100835</t>
+          <t>101069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107595</t>
+          <t>107582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114400</t>
+          <t>114335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210812</t>
+          <t>210980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218594</t>
+          <t>218597</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134668</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143485</t>
+          <t>143573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143633</t>
+          <t>144024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152106</t>
+          <t>152122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>282027</t>
+          <t>282204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293985</t>
+          <t>294347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455637</t>
+          <t>456424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468548</t>
+          <t>468370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511064</t>
+          <t>511239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525422</t>
+          <t>526014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>974114</t>
+          <t>973608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>992114</t>
+          <t>991505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100953</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191332</t>
+          <t>191341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144294</t>
+          <t>143589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150544</t>
+          <t>150535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166779</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173642</t>
+          <t>173517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>313728</t>
+          <t>313654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322652</t>
+          <t>322810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113578</t>
+          <t>113572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123665</t>
+          <t>124089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131756</t>
+          <t>131772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240622</t>
+          <t>240023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248104</t>
+          <t>248081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150665</t>
+          <t>151095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161758</t>
+          <t>161809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149227</t>
+          <t>149174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156543</t>
+          <t>156270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304221</t>
+          <t>303405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316758</t>
+          <t>316748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504197</t>
+          <t>504204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517233</t>
+          <t>517137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>552046</t>
+          <t>551223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563500</t>
+          <t>563716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059527</t>
+          <t>1059467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106314</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114005</t>
+          <t>113994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124167</t>
+          <t>124551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135410</t>
+          <t>135698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234214</t>
+          <t>234277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247437</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36780</t>
+          <t>38249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177976</t>
+          <t>177378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186317</t>
+          <t>186415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226502</t>
+          <t>226814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242671</t>
+          <t>242598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408768</t>
+          <t>407299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426755</t>
+          <t>425962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39952</t>
+          <t>39962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171849</t>
+          <t>171294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184218</t>
+          <t>185021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159115</t>
+          <t>158198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179711</t>
+          <t>179387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>335735</t>
+          <t>335725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360693</t>
+          <t>360221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154310</t>
+          <t>153882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163159</t>
+          <t>163077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169843</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178878</t>
+          <t>178849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328374</t>
+          <t>327513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340533</t>
+          <t>340225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44047</t>
+          <t>45360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>34286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>61958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100011</t>
+          <t>99037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>622108</t>
+          <t>620795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641375</t>
+          <t>639795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699552</t>
+          <t>700014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>727002</t>
+          <t>727686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1328116</t>
+          <t>1329090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362555</t>
+          <t>1364235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
